--- a/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:41:10+00:00</t>
+    <t>2024-01-29T10:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -125,7 +125,7 @@
     <t>UNK</t>
   </si>
   <si>
-    <t>FINESS d'entité juridique</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>

--- a/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-marital-status.xlsx
+++ b/ig/nr-add-marital-status-binding/ValueSet-fr-core-vs-marital-status.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:18:33+00:00</t>
+    <t>2024-01-29T10:24:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
